--- a/web/beispieldaten/kunden-standard.xlsx
+++ b/web/beispieldaten/kunden-standard.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
   <si>
     <t>Vorname</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Produkt</t>
   </si>
   <si>
+    <t>Warengruppe</t>
+  </si>
+  <si>
     <t>Kaufdatum</t>
   </si>
   <si>
@@ -64,10 +67,16 @@
     <t>Ergobag Cubo</t>
   </si>
   <si>
+    <t>Schulranzen</t>
+  </si>
+  <si>
     <t>18.07.2023</t>
   </si>
   <si>
     <t>Sporttasche Größe M</t>
+  </si>
+  <si>
+    <t>Zubehör</t>
   </si>
   <si>
     <t>02.08.2025</t>
@@ -649,13 +658,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="9" width="14" customWidth="1"/>
+    <col min="1" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,353 +694,392 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="F11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" t="s">
-        <v>84</v>
-      </c>
-      <c r="H13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" t="s">
-        <v>85</v>
+      <c r="J13" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/web/beispieldaten/kunden-standard.xlsx
+++ b/web/beispieldaten/kunden-standard.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+  <si>
+    <t>Anrede</t>
+  </si>
   <si>
     <t>Vorname</t>
   </si>
@@ -43,6 +46,9 @@
     <t>Kaufdatum</t>
   </si>
   <si>
+    <t>Frau</t>
+  </si>
+  <si>
     <t>Anna</t>
   </si>
   <si>
@@ -80,6 +86,9 @@
   </si>
   <si>
     <t>02.08.2025</t>
+  </si>
+  <si>
+    <t>Herr</t>
   </si>
   <si>
     <t>Bernd</t>
@@ -658,15 +667,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="1" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,389 +706,428 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="K5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="G5" t="s">
+      <c r="D6" t="s">
         <v>35</v>
       </c>
-      <c r="H5" t="s">
+      <c r="E6" t="s">
         <v>36</v>
       </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
       </c>
       <c r="H6" t="s">
         <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="J13" t="s">
         <v>20</v>
       </c>
-      <c r="I11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" t="s">
-        <v>88</v>
+      <c r="K13" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
